--- a/sampleprojects/Cribbage/excel/project.xlsx
+++ b/sampleprojects/Cribbage/excel/project.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
   <si>
     <t>EDD: EDD</t>
   </si>
@@ -97,18 +97,33 @@
     <t>combo</t>
   </si>
   <si>
+    <t>(5 attributes)</t>
+  </si>
+  <si>
     <t>count</t>
   </si>
   <si>
     <t>written by subsets/combinations; count, not size — SIZE is an EL keyword</t>
   </si>
   <si>
+    <t>distinct</t>
+  </si>
+  <si>
+    <t>written by suffixes: distinct stat values in the window</t>
+  </si>
+  <si>
     <t>members</t>
   </si>
   <si>
     <t>array</t>
   </si>
   <si>
+    <t>spread</t>
+  </si>
+  <si>
+    <t>written by suffixes: max minus min stat value in the window</t>
+  </si>
+  <si>
     <t>sum</t>
   </si>
   <si>
@@ -197,6 +212,42 @@
   </si>
   <si>
     <t>total</t>
+  </si>
+  <si>
+    <t>play</t>
+  </si>
+  <si>
+    <t>(10 attributes)</t>
+  </si>
+  <si>
+    <t>the current sub-round stack in lay order, newest last</t>
+  </si>
+  <si>
+    <t>running count after the newest card</t>
+  </si>
+  <si>
+    <t>count_points</t>
+  </si>
+  <si>
+    <t>go_points</t>
+  </si>
+  <si>
+    <t>is_go</t>
+  </si>
+  <si>
+    <t>this event is a go award, not a card</t>
+  </si>
+  <si>
+    <t>is_last</t>
+  </si>
+  <si>
+    <t>the newest card was the last card of the play</t>
+  </si>
+  <si>
+    <t>windows</t>
+  </si>
+  <si>
+    <t>work: trailing windows of cards, longest first</t>
   </si>
   <si>
     <t>multiplicity</t>
@@ -870,7 +921,7 @@
         <v>26</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
@@ -889,7 +940,7 @@
         <v>16</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>18</v>
@@ -907,7 +958,7 @@
         <v>20</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>16</v>
@@ -930,13 +981,13 @@
         <v>16</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="14" t="s">
         <v>30</v>
       </c>
+      <c r="C9" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="D9" s="8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>16</v>
@@ -948,7 +999,7 @@
         <v>20</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>16</v>
@@ -971,67 +1022,89 @@
         <v>16</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
+      <c r="D11" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="s">
         <v>16</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>18</v>
@@ -1049,7 +1122,7 @@
         <v>20</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>16</v>
@@ -1068,58 +1141,36 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H13" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="K13" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="M13" s="8" t="s">
-        <v>16</v>
-      </c>
+      <c r="A13" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="s">
         <v>16</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>18</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>16</v>
@@ -1150,33 +1201,55 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
+      <c r="A15" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="M15" s="8" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="s">
         <v>16</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>14</v>
@@ -1184,14 +1257,14 @@
       <c r="E16" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F16" s="15" t="s">
-        <v>19</v>
+      <c r="F16" s="7" t="s">
+        <v>16</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>20</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>16</v>
@@ -1210,70 +1283,48 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H17" s="16" t="s">
+      <c r="A17" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="I17" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="K17" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="M17" s="8" t="s">
-        <v>16</v>
-      </c>
+      <c r="B17" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="s">
         <v>16</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>18</v>
+        <v>43</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>33</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F18" s="7" t="s">
-        <v>16</v>
+      <c r="F18" s="15" t="s">
+        <v>19</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>20</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>16</v>
@@ -1296,13 +1347,13 @@
         <v>16</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>18</v>
+        <v>45</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>33</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>16</v>
@@ -1314,7 +1365,7 @@
         <v>20</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="I19" s="8" t="s">
         <v>16</v>
@@ -1337,10 +1388,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>45</v>
+        <v>47</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>18</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>16</v>
@@ -1348,14 +1399,14 @@
       <c r="E20" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F20" s="15" t="s">
-        <v>19</v>
+      <c r="F20" s="7" t="s">
+        <v>16</v>
       </c>
       <c r="G20" s="7" t="s">
         <v>20</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>16</v>
@@ -1378,25 +1429,25 @@
         <v>16</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>30</v>
+        <v>48</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>18</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E21" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F21" s="15" t="s">
-        <v>19</v>
+      <c r="F21" s="8" t="s">
+        <v>16</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>20</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="I21" s="8" t="s">
         <v>16</v>
@@ -1421,8 +1472,8 @@
       <c r="B22" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C22" s="11" t="s">
-        <v>18</v>
+      <c r="C22" s="12" t="s">
+        <v>50</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>16</v>
@@ -1430,14 +1481,14 @@
       <c r="E22" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F22" s="7" t="s">
-        <v>16</v>
+      <c r="F22" s="15" t="s">
+        <v>19</v>
       </c>
       <c r="G22" s="7" t="s">
         <v>20</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="I22" s="7" t="s">
         <v>16</v>
@@ -1460,25 +1511,25 @@
         <v>16</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>18</v>
+        <v>52</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>33</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E23" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F23" s="8" t="s">
-        <v>16</v>
+      <c r="F23" s="15" t="s">
+        <v>19</v>
       </c>
       <c r="G23" s="8" t="s">
         <v>20</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="I23" s="8" t="s">
         <v>16</v>
@@ -1501,13 +1552,13 @@
         <v>16</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>30</v>
+        <v>54</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>18</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>16</v>
@@ -1519,7 +1570,7 @@
         <v>20</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="I24" s="7" t="s">
         <v>16</v>
@@ -1542,13 +1593,13 @@
         <v>16</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>30</v>
+        <v>55</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>18</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="E25" s="8" t="s">
         <v>16</v>
@@ -1560,7 +1611,7 @@
         <v>20</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="I25" s="8" t="s">
         <v>16</v>
@@ -1585,11 +1636,11 @@
       <c r="B26" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C26" s="11" t="s">
-        <v>18</v>
+      <c r="C26" s="14" t="s">
+        <v>33</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>16</v>
@@ -1601,7 +1652,7 @@
         <v>20</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="I26" s="7" t="s">
         <v>16</v>
@@ -1624,25 +1675,25 @@
         <v>16</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>18</v>
+        <v>58</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>33</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="E27" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F27" s="15" t="s">
-        <v>19</v>
+      <c r="F27" s="8" t="s">
+        <v>16</v>
       </c>
       <c r="G27" s="8" t="s">
         <v>20</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="I27" s="8" t="s">
         <v>16</v>
@@ -1665,13 +1716,13 @@
         <v>16</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>30</v>
+        <v>61</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>18</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>16</v>
@@ -1683,7 +1734,7 @@
         <v>20</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="I28" s="7" t="s">
         <v>16</v>
@@ -1706,7 +1757,7 @@
         <v>16</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>18</v>
@@ -1717,8 +1768,8 @@
       <c r="E29" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F29" s="8" t="s">
-        <v>16</v>
+      <c r="F29" s="15" t="s">
+        <v>19</v>
       </c>
       <c r="G29" s="8" t="s">
         <v>20</v>
@@ -1743,144 +1794,655 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="6"/>
-      <c r="M30" s="6"/>
+      <c r="A30" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="I30" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J30" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L30" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="M30" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="8" t="s">
         <v>16</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C31" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D31" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G31" s="7" t="s">
+      <c r="D31" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G31" s="8" t="s">
         <v>20</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J31" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="K31" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="L31" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="M31" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K31" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="M31" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H32" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="I32" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J32" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="K32" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="L32" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="M32" s="8" t="s">
-        <v>16</v>
-      </c>
+      <c r="A32" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="6"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="s">
         <v>16</v>
       </c>
       <c r="B33" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F33" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L33" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="M33" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F34" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H34" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K34" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="L34" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="M34" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H35" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L35" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="M35" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H36" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="I36" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J36" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K36" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="L36" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="M36" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F37" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H37" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L37" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="M37" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F38" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H38" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="I38" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J38" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K38" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="L38" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="M38" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H39" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J39" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K39" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L39" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="M39" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H40" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J40" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K40" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="L40" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="M40" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B41" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="C41" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D33" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="I33" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J33" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="K33" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="L33" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="M33" s="7" t="s">
+      <c r="D41" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H41" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J41" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L41" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="M41" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H42" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="I42" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J42" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K42" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="L42" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="M42" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="6"/>
+      <c r="K43" s="6"/>
+      <c r="L43" s="6"/>
+      <c r="M43" s="6"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H44" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="I44" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J44" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K44" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L44" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="M44" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H45" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J45" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K45" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="L45" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="M45" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H46" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="I46" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J46" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K46" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L46" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="M46" s="7" t="s">
         <v>16</v>
       </c>
     </row>
